--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04cdab8faccd4391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d1e38c82a5442a8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d1e38c82a5442a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90169e327f6e4604"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90169e327f6e4604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cf3ed378b774981"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cf3ed378b774981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1a51b4c67b048f8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1a51b4c67b048f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb46c350b2c7c45a4"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb46c350b2c7c45a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05b32e740ae44c1a"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/DefinedNames/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05b32e740ae44c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc934ea62bf8f453d"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="TaxRate">Sheet1!$A$1</x:definedName>
